--- a/data/trans_orig/CoPsoQ-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/CoPsoQ-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2012</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78430</t>
+          <t>76906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105036</t>
+          <t>104978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>38599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62043</t>
+          <t>61347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>124147</t>
+          <t>123451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161407</t>
+          <t>158646</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,45%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>23833</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44860</t>
+          <t>44242</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25514</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47318</t>
+          <t>45830</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54554</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84721</t>
+          <t>84657</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41842</t>
+          <t>41272</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65871</t>
+          <t>66763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39901</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63303</t>
+          <t>63084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86855</t>
+          <t>89138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121062</t>
+          <t>122574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -1301,97 +1301,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2053</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>478656</t>
+          <t>479787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>540975</t>
+          <t>539923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>294077</t>
+          <t>295506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>342428</t>
+          <t>344545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>790900</t>
+          <t>789522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>868663</t>
+          <t>868326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151387</t>
+          <t>149600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200398</t>
+          <t>199936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100205</t>
+          <t>101584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141218</t>
+          <t>140871</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264507</t>
+          <t>264545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326782</t>
+          <t>325812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>186920</t>
+          <t>184199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>238438</t>
+          <t>239896</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106465</t>
+          <t>104654</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>147150</t>
+          <t>145461</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>304822</t>
+          <t>301507</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>368738</t>
+          <t>370967</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -1870,97 +1870,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2139</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>184417</t>
+          <t>185720</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>222172</t>
+          <t>221260</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>119050</t>
+          <t>118979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>151265</t>
+          <t>151018</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>314689</t>
+          <t>314442</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>364012</t>
+          <t>364538</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48168</t>
+          <t>47819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79278</t>
+          <t>78254</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38259</t>
+          <t>37510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63451</t>
+          <t>64537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93339</t>
+          <t>91607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133188</t>
+          <t>132386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36392</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65176</t>
+          <t>65146</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32193</t>
+          <t>31743</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57030</t>
+          <t>58762</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75135</t>
+          <t>74524</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112517</t>
+          <t>111257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -2439,97 +2439,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2079</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>766346</t>
+          <t>767387</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>848854</t>
+          <t>841109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>470451</t>
+          <t>469163</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>532328</t>
+          <t>531472</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1261123</t>
+          <t>1261492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1356725</t>
+          <t>1357079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,58%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240108</t>
+          <t>238925</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>301488</t>
+          <t>301016</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>181598</t>
+          <t>182031</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>232205</t>
+          <t>233721</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>435527</t>
+          <t>437235</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>515692</t>
+          <t>514396</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>281144</t>
+          <t>282474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>345067</t>
+          <t>347335</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>192687</t>
+          <t>194448</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>245277</t>
+          <t>247026</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>491113</t>
+          <t>492303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>574037</t>
+          <t>576331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2016</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3239,97 +3239,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57118</t>
+          <t>58678</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82474</t>
+          <t>82842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>24399</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40975</t>
+          <t>41804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87986</t>
+          <t>89557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118294</t>
+          <t>118857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>30058</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50683</t>
+          <t>51458</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24458</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43520</t>
+          <t>44389</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69836</t>
+          <t>70422</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24162</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45346</t>
+          <t>45421</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15931</t>
+          <t>15685</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31061</t>
+          <t>31245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44230</t>
+          <t>44397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69868</t>
+          <t>69966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -3808,97 +3808,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2052</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>480560</t>
+          <t>481034</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>542693</t>
+          <t>542473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>347185</t>
+          <t>348400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>395370</t>
+          <t>397281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>844217</t>
+          <t>847401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>919389</t>
+          <t>924123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>183727</t>
+          <t>182297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>234233</t>
+          <t>234031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116845</t>
+          <t>116270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162193</t>
+          <t>159472</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316058</t>
+          <t>314825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>382476</t>
+          <t>380854</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>179020</t>
+          <t>181519</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>231536</t>
+          <t>231506</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,49 +4162,49 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>25,02%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>141703</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>122717</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>163373</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>21,71%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>25,03%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141703</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>120802</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>163320</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>21,71%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>18,51%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>25,02%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>334</t>
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>316448</t>
+          <t>316603</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>382155</t>
+          <t>385769</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -4377,97 +4377,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>178383</t>
+          <t>179861</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>216695</t>
+          <t>218143</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>147496</t>
+          <t>145746</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>183111</t>
+          <t>181344</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>335614</t>
+          <t>336000</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>388361</t>
+          <t>388140</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56372</t>
+          <t>56505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89226</t>
+          <t>88808</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55081</t>
+          <t>55508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83801</t>
+          <t>85947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121329</t>
+          <t>120472</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165053</t>
+          <t>165493</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65687</t>
+          <t>64129</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97414</t>
+          <t>95886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59622</t>
+          <t>60446</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89274</t>
+          <t>91055</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133364</t>
+          <t>132344</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>178673</t>
+          <t>178379</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -4946,97 +4946,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>740031</t>
+          <t>742354</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>814908</t>
+          <t>818977</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>535742</t>
+          <t>533572</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>600394</t>
+          <t>601974</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1298251</t>
+          <t>1297177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1397407</t>
+          <t>1397409</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>288270</t>
+          <t>288647</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>352946</t>
+          <t>353813</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>196504</t>
+          <t>199974</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>250964</t>
+          <t>254996</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>497906</t>
+          <t>503544</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>586432</t>
+          <t>591638</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>287004</t>
+          <t>287818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>354791</t>
+          <t>352563</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>212698</t>
+          <t>210660</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>264667</t>
+          <t>265943</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>519566</t>
+          <t>516947</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>605198</t>
+          <t>602305</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2023</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>388568</t>
+          <t>390521</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>413608</t>
+          <t>414239</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>569581</t>
+          <t>569316</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>582536</t>
+          <t>582762</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>964199</t>
+          <t>964328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>992414</t>
+          <t>992605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>13298</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30349</t>
+          <t>30472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -5972,12 +5972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>22670</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21853</t>
+          <t>20475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27174</t>
+          <t>26678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1006526</t>
+          <t>1034932</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1767983</t>
+          <t>1770522</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1681003</t>
+          <t>1682989</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1787928</t>
+          <t>1791416</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2595368</t>
+          <t>2631054</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3519515</t>
+          <t>3511289</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70918</t>
+          <t>71262</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136913</t>
+          <t>135389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78139</t>
+          <t>75956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133863</t>
+          <t>133549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162711</t>
+          <t>169773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>256700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48803</t>
+          <t>50572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103455</t>
+          <t>102116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>41357</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76357</t>
+          <t>76168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105468</t>
+          <t>106332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168448</t>
+          <t>172134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83945</t>
+          <t>83520</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>934956</t>
+          <t>896664</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40397</t>
+          <t>39263</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75623</t>
+          <t>75083</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>134802</t>
+          <t>138790</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1140270</t>
+          <t>1112627</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>449325</t>
+          <t>445927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>491555</t>
+          <t>492481</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>479327</t>
+          <t>479984</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>511605</t>
+          <t>512342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>936597</t>
+          <t>938964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>993896</t>
+          <t>993784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35922</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66611</t>
+          <t>69322</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30613</t>
+          <t>31242</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52780</t>
+          <t>52583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>72841</t>
+          <t>72098</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>110535</t>
+          <t>109672</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21123</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>47360</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29590</t>
+          <t>29987</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40430</t>
+          <t>40391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67721</t>
+          <t>69305</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32187</t>
+          <t>32256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60100</t>
+          <t>60540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32479</t>
+          <t>31769</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56463</t>
+          <t>55065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70680</t>
+          <t>69998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108152</t>
+          <t>108420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1845676</t>
+          <t>1837590</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2647542</t>
+          <t>2650907</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2752897</t>
+          <t>2757924</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2872086</t>
+          <t>2873956</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4522477</t>
+          <t>4472241</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5457507</t>
+          <t>5460815</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>121859</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201986</t>
+          <t>198172</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125037</t>
+          <t>121305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>188654</t>
+          <t>186463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>273887</t>
+          <t>278954</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>369065</t>
+          <t>374417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91209</t>
+          <t>89504</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>150925</t>
+          <t>149647</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64984</t>
+          <t>65462</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>100637</t>
+          <t>102267</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>171763</t>
+          <t>169534</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>241728</t>
+          <t>241849</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138098</t>
+          <t>138497</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1028973</t>
+          <t>1028565</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82643</t>
+          <t>80573</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129360</t>
+          <t>126983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>243267</t>
+          <t>240642</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1264794</t>
+          <t>1305755</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CoPsoQ-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/CoPsoQ-Estudios-trans_orig.xlsx
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76906</t>
+          <t>79945</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104978</t>
+          <t>106801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38599</t>
+          <t>37667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61347</t>
+          <t>60781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123451</t>
+          <t>122520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158646</t>
+          <t>159795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23833</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44242</t>
+          <t>43917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25514</t>
+          <t>25552</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45830</t>
+          <t>47449</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>55215</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84657</t>
+          <t>83509</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41272</t>
+          <t>41238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66763</t>
+          <t>65345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40036</t>
+          <t>40813</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63084</t>
+          <t>64143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89138</t>
+          <t>88947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122574</t>
+          <t>122315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>479787</t>
+          <t>479924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>539923</t>
+          <t>542796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>295506</t>
+          <t>293627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>344545</t>
+          <t>340076</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>789522</t>
+          <t>791433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>868326</t>
+          <t>868204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149600</t>
+          <t>152094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>199936</t>
+          <t>200509</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101584</t>
+          <t>102708</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140871</t>
+          <t>140946</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264545</t>
+          <t>264686</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325812</t>
+          <t>326317</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>184199</t>
+          <t>186231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>239896</t>
+          <t>238418</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104654</t>
+          <t>105060</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145461</t>
+          <t>146931</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>301507</t>
+          <t>302725</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>370967</t>
+          <t>370642</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>185720</t>
+          <t>184472</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>221260</t>
+          <t>221900</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>118979</t>
+          <t>119324</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>151018</t>
+          <t>149784</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>314442</t>
+          <t>316390</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>364538</t>
+          <t>362434</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47819</t>
+          <t>46688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78254</t>
+          <t>78397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37510</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91607</t>
+          <t>92635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132386</t>
+          <t>132947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35752</t>
+          <t>36269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65146</t>
+          <t>63477</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31743</t>
+          <t>32597</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58762</t>
+          <t>57215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74524</t>
+          <t>74829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111257</t>
+          <t>111661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>767387</t>
+          <t>770136</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>841109</t>
+          <t>844662</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>469163</t>
+          <t>472904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>531472</t>
+          <t>533501</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1261492</t>
+          <t>1258677</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357079</t>
+          <t>1354155</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>238925</t>
+          <t>238043</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>301016</t>
+          <t>299201</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>182031</t>
+          <t>181460</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>233721</t>
+          <t>231498</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>437235</t>
+          <t>437594</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>514396</t>
+          <t>518193</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>282474</t>
+          <t>285519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>347335</t>
+          <t>349840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>194448</t>
+          <t>191835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>247026</t>
+          <t>242941</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>492303</t>
+          <t>492317</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>576331</t>
+          <t>576913</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58678</t>
+          <t>57450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82842</t>
+          <t>82034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24399</t>
+          <t>24715</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41804</t>
+          <t>40564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89557</t>
+          <t>88105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118857</t>
+          <t>117448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30058</t>
+          <t>30425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51458</t>
+          <t>53486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44389</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70422</t>
+          <t>69648</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24835</t>
+          <t>24354</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45421</t>
+          <t>45824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31245</t>
+          <t>30739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44397</t>
+          <t>43648</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69966</t>
+          <t>69223</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>481034</t>
+          <t>482553</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>542473</t>
+          <t>545960</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>348400</t>
+          <t>346523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>397281</t>
+          <t>398368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>847401</t>
+          <t>841709</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>924123</t>
+          <t>921252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>182297</t>
+          <t>183612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>234031</t>
+          <t>235260</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116270</t>
+          <t>119646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159472</t>
+          <t>161630</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314825</t>
+          <t>315527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>380854</t>
+          <t>384738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>181519</t>
+          <t>181352</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>231506</t>
+          <t>233949</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122717</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163373</t>
+          <t>161662</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>316603</t>
+          <t>313311</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385769</t>
+          <t>377554</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>179861</t>
+          <t>177642</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>218143</t>
+          <t>215623</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>145746</t>
+          <t>148689</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181344</t>
+          <t>182850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>336000</t>
+          <t>335940</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>388140</t>
+          <t>388513</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,95%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56505</t>
+          <t>59198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88808</t>
+          <t>90951</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55508</t>
+          <t>54921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85947</t>
+          <t>85470</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120472</t>
+          <t>120698</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165493</t>
+          <t>165376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64129</t>
+          <t>61994</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95886</t>
+          <t>96201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60446</t>
+          <t>60890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91055</t>
+          <t>90181</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132344</t>
+          <t>133697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>178379</t>
+          <t>178017</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>742354</t>
+          <t>736420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>818977</t>
+          <t>813501</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>533572</t>
+          <t>538271</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>601974</t>
+          <t>602786</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1297177</t>
+          <t>1300096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1397409</t>
+          <t>1398335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>288647</t>
+          <t>288619</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>353813</t>
+          <t>351692</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>199974</t>
+          <t>199014</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>254996</t>
+          <t>251222</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>503544</t>
+          <t>506484</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>591638</t>
+          <t>587367</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>287818</t>
+          <t>289766</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>352563</t>
+          <t>355467</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>210660</t>
+          <t>212626</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>265943</t>
+          <t>266260</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>516947</t>
+          <t>517700</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>602305</t>
+          <t>599908</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -5741,32 +5741,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>403697</t>
+          <t>452932</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>390521</t>
+          <t>435824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>414239</t>
+          <t>465388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5776,32 +5776,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>576982</t>
+          <t>628530</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>569316</t>
+          <t>619905</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>582762</t>
+          <t>635304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5811,32 +5811,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>980679</t>
+          <t>1081462</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>964328</t>
+          <t>1060663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>992605</t>
+          <t>1096160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -5854,32 +5854,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>11488</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5889,32 +5889,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>8165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>19577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5924,32 +5924,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>24290</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13298</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -5967,32 +5967,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6002,32 +6002,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6037,32 +6037,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -6080,32 +6080,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>19863</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>35942</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6115,27 +6115,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6150,32 +6150,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>26305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>45314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -6193,17 +6193,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>436639</t>
+          <t>494361</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>436639</t>
+          <t>494361</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>436639</t>
+          <t>494361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,17 +6228,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>595185</t>
+          <t>652149</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>595185</t>
+          <t>652149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>595185</t>
+          <t>652149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,17 +6263,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1031824</t>
+          <t>1146510</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1031824</t>
+          <t>1146510</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1031824</t>
+          <t>1146510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6310,32 +6310,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1551916</t>
+          <t>1694229</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1034932</t>
+          <t>1658485</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1770522</t>
+          <t>1733799</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6345,32 +6345,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1725061</t>
+          <t>1591227</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1682989</t>
+          <t>1564607</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1791416</t>
+          <t>1618547</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6380,32 +6380,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3276977</t>
+          <t>3285456</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2631054</t>
+          <t>3237347</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3511289</t>
+          <t>3332436</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>
@@ -6423,32 +6423,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>107001</t>
+          <t>121486</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71262</t>
+          <t>96615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135389</t>
+          <t>147413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6458,32 +6458,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>108752</t>
+          <t>119306</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75956</t>
+          <t>99855</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133549</t>
+          <t>141553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6493,32 +6493,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>215753</t>
+          <t>240792</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169773</t>
+          <t>212204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256700</t>
+          <t>278434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -6536,32 +6536,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78351</t>
+          <t>83545</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50572</t>
+          <t>64748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102116</t>
+          <t>104361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6571,32 +6571,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59991</t>
+          <t>66630</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>54380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76168</t>
+          <t>82469</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6606,32 +6606,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>138342</t>
+          <t>150175</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106332</t>
+          <t>124970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>172134</t>
+          <t>173516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -6649,32 +6649,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>325155</t>
+          <t>89324</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83520</t>
+          <t>70922</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>896664</t>
+          <t>113813</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6684,32 +6684,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58091</t>
+          <t>66440</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39263</t>
+          <t>53999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75083</t>
+          <t>82956</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6719,32 +6719,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>383247</t>
+          <t>155764</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>138790</t>
+          <t>133602</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1112627</t>
+          <t>184308</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -6762,17 +6762,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2062423</t>
+          <t>1988584</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2062423</t>
+          <t>1988584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2062423</t>
+          <t>1988584</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,17 +6797,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1951896</t>
+          <t>1843603</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1951896</t>
+          <t>1843603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1951896</t>
+          <t>1843603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,17 +6832,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4014319</t>
+          <t>3832187</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4014319</t>
+          <t>3832187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4014319</t>
+          <t>3832187</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6879,32 +6879,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>470244</t>
+          <t>514833</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>445927</t>
+          <t>489211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>492481</t>
+          <t>537067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6914,32 +6914,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>497004</t>
+          <t>556431</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>479984</t>
+          <t>535880</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512342</t>
+          <t>572448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>967248</t>
+          <t>1071263</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>938964</t>
+          <t>1040487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>993784</t>
+          <t>1100313</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -6992,32 +6992,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>54875</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36484</t>
+          <t>39996</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69322</t>
+          <t>74381</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7027,32 +7027,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40597</t>
+          <t>45977</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31242</t>
+          <t>35832</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52583</t>
+          <t>59291</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7062,32 +7062,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>90217</t>
+          <t>100852</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>72098</t>
+          <t>82319</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>109672</t>
+          <t>123405</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -7105,32 +7105,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31710</t>
+          <t>37892</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>26631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47360</t>
+          <t>52877</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7140,67 +7140,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21544</t>
+          <t>23249</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29987</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>61141</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>47444</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>77843</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>3,58%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>53253</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>40391</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>69305</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -7218,32 +7218,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43885</t>
+          <t>47174</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32256</t>
+          <t>34197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60540</t>
+          <t>63428</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7253,32 +7253,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42708</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31769</t>
+          <t>34021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55065</t>
+          <t>59576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7288,32 +7288,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>86593</t>
+          <t>92274</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69998</t>
+          <t>74464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108420</t>
+          <t>114339</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -7331,17 +7331,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>595459</t>
+          <t>654774</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>595459</t>
+          <t>654774</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>595459</t>
+          <t>654774</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,17 +7366,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>601853</t>
+          <t>670757</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>601853</t>
+          <t>670757</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>601853</t>
+          <t>670757</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,17 +7401,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1197312</t>
+          <t>1325530</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1197312</t>
+          <t>1325530</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1197312</t>
+          <t>1325530</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7448,32 +7448,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2425856</t>
+          <t>2661994</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1837590</t>
+          <t>2615334</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2650907</t>
+          <t>2708765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,32 +7483,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2799048</t>
+          <t>2776188</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2757924</t>
+          <t>2743060</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2873956</t>
+          <t>2807005</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,32 +7518,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5224904</t>
+          <t>5438181</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4472241</t>
+          <t>5379470</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5460815</t>
+          <t>5490250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -7561,32 +7561,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>166031</t>
+          <t>187850</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121859</t>
+          <t>156734</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198172</t>
+          <t>221881</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7596,32 +7596,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>159664</t>
+          <t>178084</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>121305</t>
+          <t>156811</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186463</t>
+          <t>204076</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7631,32 +7631,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>325695</t>
+          <t>365934</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>278954</t>
+          <t>330748</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>374417</t>
+          <t>408825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -7674,32 +7674,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>121117</t>
+          <t>131514</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89504</t>
+          <t>109346</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>149647</t>
+          <t>160821</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7709,32 +7709,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>83729</t>
+          <t>94255</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65462</t>
+          <t>78757</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102267</t>
+          <t>114441</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7744,32 +7744,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>204845</t>
+          <t>225769</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169534</t>
+          <t>197890</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>241849</t>
+          <t>259265</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -7787,32 +7787,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>381516</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138497</t>
+          <t>128400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1028565</t>
+          <t>185479</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7822,32 +7822,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>106494</t>
+          <t>117982</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80573</t>
+          <t>99252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126983</t>
+          <t>139220</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>488010</t>
+          <t>274343</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>240642</t>
+          <t>242981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1305755</t>
+          <t>313235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7900,17 +7900,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3094520</t>
+          <t>3137719</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3094520</t>
+          <t>3137719</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3094520</t>
+          <t>3137719</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7935,17 +7935,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3148934</t>
+          <t>3166509</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3148934</t>
+          <t>3166509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3148934</t>
+          <t>3166509</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7970,17 +7970,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6243454</t>
+          <t>6304227</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6243454</t>
+          <t>6304227</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6243454</t>
+          <t>6304227</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
